--- a/sheets/민요/검수/함양 양잠가.xlsx
+++ b/sheets/민요/검수/함양 양잠가.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +131,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3316,8 +3375,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -3332,826 +3395,761 @@
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">함양 양잠가 — 민요채보-1/함양 양잠가.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">함양 양잠가</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">죽</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="L3" s="9"/>
+      <c r="M3" s="12"/>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E4" s="12"/>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G4" s="12"/>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I4" s="12"/>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K4" s="12"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="12"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">죽</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L5" s="9"/>
+      <c r="M5" s="12"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I6" s="12"/>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="L6" s="9"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 ·</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">죽
 潢
 無</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢
 姑</t>
         </is>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" s="12"/>
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">죽</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="L7" s="9"/>
+      <c r="M7" s="12"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I8" s="12"/>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K8" s="12"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="12"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="12"/>
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 南</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 姑</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" s="12"/>
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="L9" s="9"/>
+      <c r="M9" s="12"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="C10" s="12"/>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E10" s="12"/>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I10" s="12"/>
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="K10" s="12"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="12"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 湳
 潢</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="C11" s="12"/>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E11" s="12"/>
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢
 姑</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢
 姑</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">살</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="L11" s="9"/>
+      <c r="M11" s="12"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G12" s="12"/>
+      <c r="H12" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="I12" s="12"/>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K12" s="12"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="12"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">혜</t>
         </is>
       </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="L13" s="9"/>
+      <c r="M13" s="12"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E14" s="12"/>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G14" s="12"/>
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="I14" s="12"/>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K14" s="12"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="12"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">된</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">된</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢
 姑</t>
         </is>
       </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G15" s="12"/>
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="I15" s="12"/>
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="K15" s="12"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="12"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E16" s="12"/>
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="G16" s="12"/>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I16" s="12"/>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K16" s="12"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="12"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="G17" s="12"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 姑</t>
         </is>
       </c>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="K17" s="12"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="12"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="E18" s="12"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="12"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:M2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/함양 양잠가.xlsx
+++ b/sheets/민요/검수/함양 양잠가.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑―</t>
+          <t xml:space="preserve">姑–</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑―</t>
+          <t xml:space="preserve">姑–</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑―</t>
+          <t xml:space="preserve">姑–</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑―</t>
+          <t xml:space="preserve">姑–</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰―</t>
+          <t xml:space="preserve">汰–</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰―</t>
+          <t xml:space="preserve">汰–</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢</t>
+          <t xml:space="preserve">–潢</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢</t>
+          <t xml:space="preserve">–潢</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰―</t>
+          <t xml:space="preserve">汰–</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰―</t>
+          <t xml:space="preserve">汰–</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢―</t>
+          <t xml:space="preserve">潢–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢―</t>
+          <t xml:space="preserve">潢–</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑―</t>
+          <t xml:space="preserve">姑–</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑―</t>
+          <t xml:space="preserve">姑–</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑―</t>
+          <t xml:space="preserve">姑–</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑―</t>
+          <t xml:space="preserve">姑–</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·―</t>
+          <t xml:space="preserve">·–</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·―</t>
+          <t xml:space="preserve">·–</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑―</t>
+          <t xml:space="preserve">姑–</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="H3" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑―</t>
+          <t xml:space="preserve">姑–</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰―</t>
+          <t xml:space="preserve">汰–</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑―</t>
+          <t xml:space="preserve">姑–</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2948,7 +2948,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">·―</t>
+          <t xml:space="preserve">·–</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢―</t>
+          <t xml:space="preserve">潢–</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑―</t>
+          <t xml:space="preserve">姑–</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰―</t>
+          <t xml:space="preserve">汰–</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3240,7 +3240,7 @@
       <c r="A16" s="0"/>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3258,7 +3258,7 @@
       <c r="G16" s="2"/>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢</t>
+          <t xml:space="preserve">–潢</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">

--- a/sheets/민요/검수/함양 양잠가.xlsx
+++ b/sheets/민요/검수/함양 양잠가.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2716,628 +2745,628 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">함양 양잠가</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑–</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑·</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">등</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑–</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J3" s="17"/>
-      <c r="K3" s="2"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="22"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="E4" s="22"/>
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑·</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">등가</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑·</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="J4" s="17"/>
-      <c r="K4" s="2"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="22"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑··</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢·</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰潢</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑·</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">더</t>
         </is>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="2"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="22"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="E6" s="22"/>
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">실실</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="J6" s="17"/>
-      <c r="K6" s="2"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="22"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">죽</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰–</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">죽우</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑–</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="2"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="22"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·–</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="22"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">불러</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">헤이</t>
         </is>
       </c>
-      <c r="J8" s="17"/>
-      <c r="K8" s="2"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="22"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">죽</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢–</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑··</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="J9" s="17"/>
-      <c r="K9" s="2"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="22"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어서</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="22"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑△</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="22"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="2"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="22"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢潢</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아이</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑–</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="F11" s="21"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢·</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J11" s="17"/>
-      <c r="K11" s="2"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="22"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑無</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아이가</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="E12" s="22"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="2"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">첩</t>
         </is>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="F13" s="21"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰–</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="J13" s="17"/>
-      <c r="K13" s="2"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="22"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">바람</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="E14" s="22"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢淋</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">두</t>
         </is>
       </c>
-      <c r="J14" s="17"/>
-      <c r="K14" s="2"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="22"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無姑</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">될</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">청산에</t>
         </is>
       </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="F15" s="21"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢淋</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">견</t>
         </is>
       </c>
-      <c r="J15" s="17"/>
-      <c r="K15" s="2"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="22"/>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">거</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="E16" s="22"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–潢</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J16" s="17"/>
-      <c r="K16" s="2"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="22"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑··</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">고드름</t>
         </is>
       </c>
-      <c r="F17" s="17"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="F17" s="21"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">울음</t>
         </is>
       </c>
-      <c r="J17" s="17"/>
-      <c r="K17" s="2"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="22"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="22"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">되거라</t>
         </is>
       </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="F18" s="21"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢姑</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">운다</t>
         </is>
       </c>
-      <c r="J18" s="17"/>
-      <c r="K18" s="2"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/함양 양잠가.xlsx
+++ b/sheets/민요/검수/함양 양잠가.xlsx
@@ -2728,22 +2728,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="29.14" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="29.14" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑·</t>
+          <t xml:space="preserve">姑–</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2805,7 +2805,7 @@
       <c r="J3" s="21"/>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="29.14" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2819,13 +2819,13 @@
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="22"/>
       <c r="F4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑姑·</t>
+          <t xml:space="preserve">姑姑–</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑·</t>
+          <t xml:space="preserve">姑–</t>
         </is>
       </c>
       <c r="I4" s="22" t="inlineStr">
@@ -2846,11 +2846,11 @@
       <c r="J4" s="21"/>
       <c r="K4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="29.14" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑··</t>
+          <t xml:space="preserve">姑––</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢·</t>
+          <t xml:space="preserve">潢–</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑姑·</t>
+          <t xml:space="preserve">姑姑–</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr">
@@ -2891,7 +2891,7 @@
       <c r="J5" s="21"/>
       <c r="K5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="29.14" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
       <c r="C6" s="22"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E6" s="22"/>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
@@ -2928,7 +2928,7 @@
       <c r="J6" s="21"/>
       <c r="K6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="29.14" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2973,11 +2973,11 @@
       <c r="J7" s="21"/>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="29.14" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·–</t>
+          <t xml:space="preserve">––</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -3014,7 +3014,7 @@
       <c r="J8" s="21"/>
       <c r="K8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="29.14" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑··</t>
+          <t xml:space="preserve">姑––</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -3059,7 +3059,7 @@
       <c r="J9" s="21"/>
       <c r="K9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="29.14" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
       <c r="J10" s="21"/>
       <c r="K10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="29.14" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
       <c r="G11" s="22"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢·</t>
+          <t xml:space="preserve">潢–</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -3129,7 +3129,7 @@
       <c r="J11" s="21"/>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="29.14" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
       <c r="G12" s="22"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I12" s="22"/>
       <c r="J12" s="21"/>
       <c r="K12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="29.14" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
       <c r="J13" s="21"/>
       <c r="K13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="29.14" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
       <c r="J14" s="21"/>
       <c r="K14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="29.14" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="29.14" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -3298,11 +3298,11 @@
       <c r="J16" s="21"/>
       <c r="K16" s="22"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="29.14" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑··</t>
+          <t xml:space="preserve">姑––</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -3335,7 +3335,7 @@
       <c r="J17" s="21"/>
       <c r="K17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="29.14" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/함양 양잠가.xlsx
+++ b/sheets/민요/검수/함양 양잠가.xlsx
@@ -2743,7 +2743,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="29.14" customHeight="1">
+    <row r="2" ht="43.99" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="29.14" customHeight="1">
+    <row r="3" ht="43.99" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
       <c r="J3" s="21"/>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="29.14" customHeight="1">
+    <row r="4" ht="43.99" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2830,7 +2830,8 @@
       </c>
       <c r="G4" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">등가</t>
+          <t xml:space="preserve">등
+가</t>
         </is>
       </c>
       <c r="H4" s="21" t="inlineStr">
@@ -2846,7 +2847,7 @@
       <c r="J4" s="21"/>
       <c r="K4" s="22"/>
     </row>
-    <row r="5" ht="29.14" customHeight="1">
+    <row r="5" ht="43.99" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2891,7 +2892,7 @@
       <c r="J5" s="21"/>
       <c r="K5" s="22"/>
     </row>
-    <row r="6" ht="29.14" customHeight="1">
+    <row r="6" ht="43.99" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2912,7 +2913,8 @@
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">실실</t>
+          <t xml:space="preserve">실
+실</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -2928,7 +2930,7 @@
       <c r="J6" s="21"/>
       <c r="K6" s="22"/>
     </row>
-    <row r="7" ht="29.14" customHeight="1">
+    <row r="7" ht="43.99" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2947,7 +2949,8 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">죽우</t>
+          <t xml:space="preserve">죽
+우</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -2973,7 +2976,7 @@
       <c r="J7" s="21"/>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="29.14" customHeight="1">
+    <row r="8" ht="43.99" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2998,7 +3001,8 @@
       </c>
       <c r="G8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">불러</t>
+          <t xml:space="preserve">불
+러</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -3008,13 +3012,14 @@
       </c>
       <c r="I8" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">헤이</t>
+          <t xml:space="preserve">헤
+이</t>
         </is>
       </c>
       <c r="J8" s="21"/>
       <c r="K8" s="22"/>
     </row>
-    <row r="9" ht="29.14" customHeight="1">
+    <row r="9" ht="43.99" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3059,7 +3064,7 @@
       <c r="J9" s="21"/>
       <c r="K9" s="22"/>
     </row>
-    <row r="10" ht="29.14" customHeight="1">
+    <row r="10" ht="43.99" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -3068,7 +3073,8 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">어서</t>
+          <t xml:space="preserve">어
+서</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -3092,7 +3098,7 @@
       <c r="J10" s="21"/>
       <c r="K10" s="22"/>
     </row>
-    <row r="11" ht="29.14" customHeight="1">
+    <row r="11" ht="43.99" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -3101,7 +3107,8 @@
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">아이</t>
+          <t xml:space="preserve">아
+이</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -3129,7 +3136,7 @@
       <c r="J11" s="21"/>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="29.14" customHeight="1">
+    <row r="12" ht="43.99" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3138,7 +3145,9 @@
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">아이가</t>
+          <t xml:space="preserve">아
+이
+가</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -3158,7 +3167,7 @@
       <c r="J12" s="21"/>
       <c r="K12" s="22"/>
     </row>
-    <row r="13" ht="29.14" customHeight="1">
+    <row r="13" ht="43.99" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3195,7 +3204,7 @@
       <c r="J13" s="21"/>
       <c r="K13" s="22"/>
     </row>
-    <row r="14" ht="29.14" customHeight="1">
+    <row r="14" ht="43.99" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3204,7 +3213,8 @@
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">바람</t>
+          <t xml:space="preserve">바
+람</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -3228,7 +3238,7 @@
       <c r="J14" s="21"/>
       <c r="K14" s="22"/>
     </row>
-    <row r="15" ht="29.14" customHeight="1">
+    <row r="15" ht="43.99" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -3247,7 +3257,9 @@
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">청산에</t>
+          <t xml:space="preserve">청
+산
+에</t>
         </is>
       </c>
       <c r="F15" s="21"/>
@@ -3265,7 +3277,7 @@
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="29.14" customHeight="1">
+    <row r="16" ht="43.99" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -3298,7 +3310,7 @@
       <c r="J16" s="21"/>
       <c r="K16" s="22"/>
     </row>
-    <row r="17" ht="29.14" customHeight="1">
+    <row r="17" ht="43.99" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -3317,7 +3329,9 @@
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">고드름</t>
+          <t xml:space="preserve">고
+드
+름</t>
         </is>
       </c>
       <c r="F17" s="21"/>
@@ -3329,13 +3343,14 @@
       </c>
       <c r="I17" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">울음</t>
+          <t xml:space="preserve">울
+음</t>
         </is>
       </c>
       <c r="J17" s="21"/>
       <c r="K17" s="22"/>
     </row>
-    <row r="18" ht="29.14" customHeight="1">
+    <row r="18" ht="43.99" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -3350,7 +3365,9 @@
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">되거라</t>
+          <t xml:space="preserve">되
+거
+라</t>
         </is>
       </c>
       <c r="F18" s="21"/>
@@ -3362,7 +3379,8 @@
       </c>
       <c r="I18" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">운다</t>
+          <t xml:space="preserve">운
+다</t>
         </is>
       </c>
       <c r="J18" s="21"/>

--- a/sheets/민요/검수/함양 양잠가.xlsx
+++ b/sheets/민요/검수/함양 양잠가.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -224,6 +229,12 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2767,7 +2778,7 @@
           <t xml:space="preserve">姑–</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -2777,7 +2788,7 @@
           <t xml:space="preserve">姑–</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
@@ -2787,7 +2798,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">등</t>
         </is>
@@ -2797,13 +2808,13 @@
           <t xml:space="preserve">姑–</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="J3" s="21"/>
-      <c r="K3" s="22"/>
+      <c r="K3" s="25"/>
     </row>
     <row r="4" ht="43.99" customHeight="1">
       <c r="A4" s="0"/>
@@ -2812,7 +2823,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2822,13 +2833,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="22"/>
+      <c r="E4" s="25"/>
       <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑–</t>
         </is>
       </c>
-      <c r="G4" s="24" t="inlineStr">
+      <c r="G4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">등
 가</t>
@@ -2839,13 +2850,13 @@
           <t xml:space="preserve">姑–</t>
         </is>
       </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
       <c r="J4" s="21"/>
-      <c r="K4" s="22"/>
+      <c r="K4" s="25"/>
     </row>
     <row r="5" ht="43.99" customHeight="1">
       <c r="A5" s="0"/>
@@ -2854,7 +2865,7 @@
           <t xml:space="preserve">姑––</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -2864,7 +2875,7 @@
           <t xml:space="preserve">潢–</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -2874,7 +2885,7 @@
           <t xml:space="preserve">潢汰潢</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2884,13 +2895,13 @@
           <t xml:space="preserve">姑姑–</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">더</t>
         </is>
       </c>
       <c r="J5" s="21"/>
-      <c r="K5" s="22"/>
+      <c r="K5" s="25"/>
     </row>
     <row r="6" ht="43.99" customHeight="1">
       <c r="A6" s="0"/>
@@ -2899,19 +2910,19 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="25"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="25"/>
       <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">실
 실</t>
@@ -2922,13 +2933,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
       <c r="J6" s="21"/>
-      <c r="K6" s="22"/>
+      <c r="K6" s="25"/>
     </row>
     <row r="7" ht="43.99" customHeight="1">
       <c r="A7" s="0"/>
@@ -2937,7 +2948,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">죽</t>
         </is>
@@ -2947,7 +2958,7 @@
           <t xml:space="preserve">汰–</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">죽
 우</t>
@@ -2958,7 +2969,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
@@ -2968,13 +2979,13 @@
           <t xml:space="preserve">姑–</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="J7" s="21"/>
-      <c r="K7" s="22"/>
+      <c r="K7" s="25"/>
     </row>
     <row r="8" ht="43.99" customHeight="1">
       <c r="A8" s="0"/>
@@ -2983,7 +2994,7 @@
           <t xml:space="preserve">––</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
@@ -2993,13 +3004,13 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E8" s="22"/>
+      <c r="E8" s="25"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">불
 러</t>
@@ -3010,14 +3021,14 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">헤
 이</t>
         </is>
       </c>
       <c r="J8" s="21"/>
-      <c r="K8" s="22"/>
+      <c r="K8" s="25"/>
     </row>
     <row r="9" ht="43.99" customHeight="1">
       <c r="A9" s="0"/>
@@ -3026,7 +3037,7 @@
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">죽</t>
         </is>
@@ -3036,7 +3047,7 @@
           <t xml:space="preserve">潢–</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -3046,7 +3057,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -3056,13 +3067,13 @@
           <t xml:space="preserve">姑––</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
       <c r="J9" s="21"/>
-      <c r="K9" s="22"/>
+      <c r="K9" s="25"/>
     </row>
     <row r="10" ht="43.99" customHeight="1">
       <c r="A10" s="0"/>
@@ -3071,7 +3082,7 @@
           <t xml:space="preserve">無姑</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">어
 서</t>
@@ -3082,21 +3093,21 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="22"/>
+      <c r="E10" s="25"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑△</t>
         </is>
       </c>
-      <c r="G10" s="22"/>
+      <c r="G10" s="25"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I10" s="22"/>
+      <c r="I10" s="25"/>
       <c r="J10" s="21"/>
-      <c r="K10" s="22"/>
+      <c r="K10" s="25"/>
     </row>
     <row r="11" ht="43.99" customHeight="1">
       <c r="A11" s="0"/>
@@ -3105,7 +3116,7 @@
           <t xml:space="preserve">潢潢潢</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 이</t>
@@ -3116,25 +3127,25 @@
           <t xml:space="preserve">姑–</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
       <c r="F11" s="21"/>
-      <c r="G11" s="22"/>
+      <c r="G11" s="25"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢–</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="J11" s="21"/>
-      <c r="K11" s="22"/>
+      <c r="K11" s="25"/>
     </row>
     <row r="12" ht="43.99" customHeight="1">
       <c r="A12" s="0"/>
@@ -3143,7 +3154,7 @@
           <t xml:space="preserve">姑無</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 이
@@ -3155,17 +3166,17 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="25"/>
       <c r="F12" s="21"/>
-      <c r="G12" s="22"/>
+      <c r="G12" s="25"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I12" s="22"/>
+      <c r="I12" s="25"/>
       <c r="J12" s="21"/>
-      <c r="K12" s="22"/>
+      <c r="K12" s="25"/>
     </row>
     <row r="13" ht="43.99" customHeight="1">
       <c r="A13" s="0"/>
@@ -3174,7 +3185,7 @@
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
@@ -3184,25 +3195,25 @@
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">첩</t>
         </is>
       </c>
       <c r="F13" s="21"/>
-      <c r="G13" s="22"/>
+      <c r="G13" s="25"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰–</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
       <c r="J13" s="21"/>
-      <c r="K13" s="22"/>
+      <c r="K13" s="25"/>
     </row>
     <row r="14" ht="43.99" customHeight="1">
       <c r="A14" s="0"/>
@@ -3211,7 +3222,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">바
 람</t>
@@ -3222,21 +3233,21 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E14" s="22"/>
+      <c r="E14" s="25"/>
       <c r="F14" s="21"/>
-      <c r="G14" s="22"/>
+      <c r="G14" s="25"/>
       <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢淋</t>
         </is>
       </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="I14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">두</t>
         </is>
       </c>
       <c r="J14" s="21"/>
-      <c r="K14" s="22"/>
+      <c r="K14" s="25"/>
     </row>
     <row r="15" ht="43.99" customHeight="1">
       <c r="A15" s="0"/>
@@ -3245,7 +3256,7 @@
           <t xml:space="preserve">潢無姑</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">될</t>
         </is>
@@ -3255,7 +3266,7 @@
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">청
 산
@@ -3263,19 +3274,19 @@
         </is>
       </c>
       <c r="F15" s="21"/>
-      <c r="G15" s="22"/>
+      <c r="G15" s="25"/>
       <c r="H15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢淋</t>
         </is>
       </c>
-      <c r="I15" s="24" t="inlineStr">
+      <c r="I15" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">견</t>
         </is>
       </c>
       <c r="J15" s="21"/>
-      <c r="K15" s="22"/>
+      <c r="K15" s="25"/>
     </row>
     <row r="16" ht="43.99" customHeight="1">
       <c r="A16" s="0"/>
@@ -3284,7 +3295,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">거</t>
         </is>
@@ -3294,21 +3305,21 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E16" s="22"/>
+      <c r="E16" s="25"/>
       <c r="F16" s="21"/>
-      <c r="G16" s="22"/>
+      <c r="G16" s="25"/>
       <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–潢</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
       <c r="J16" s="21"/>
-      <c r="K16" s="22"/>
+      <c r="K16" s="25"/>
     </row>
     <row r="17" ht="43.99" customHeight="1">
       <c r="A17" s="0"/>
@@ -3317,7 +3328,7 @@
           <t xml:space="preserve">姑––</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -3327,7 +3338,7 @@
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">고
 드
@@ -3335,20 +3346,20 @@
         </is>
       </c>
       <c r="F17" s="21"/>
-      <c r="G17" s="22"/>
+      <c r="G17" s="25"/>
       <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">울
 음</t>
         </is>
       </c>
       <c r="J17" s="21"/>
-      <c r="K17" s="22"/>
+      <c r="K17" s="25"/>
     </row>
     <row r="18" ht="43.99" customHeight="1">
       <c r="A18" s="0"/>
@@ -3357,13 +3368,13 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C18" s="22"/>
+      <c r="C18" s="25"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">되
 거
@@ -3371,20 +3382,20 @@
         </is>
       </c>
       <c r="F18" s="21"/>
-      <c r="G18" s="22"/>
+      <c r="G18" s="25"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢姑</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="I18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">운
 다</t>
         </is>
       </c>
       <c r="J18" s="21"/>
-      <c r="K18" s="22"/>
+      <c r="K18" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/함양 양잠가.xlsx
+++ b/sheets/민요/검수/함양 양잠가.xlsx
@@ -683,10 +683,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/함양 양잠가.xlsx
+++ b/sheets/민요/검수/함양 양잠가.xlsx
@@ -504,34 +504,9 @@
 실</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+    <t xml:space="preserve">南
+–
+南</t>
   </si>
   <si>
     <t xml:space="preserve">더
@@ -624,17 +599,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -756,7 +731,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -814,6 +789,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2162,224 +2181,224 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:I10"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="54.79" customHeight="true">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="122.25" customHeight="true">
+      <c r="B3" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="19" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="122.25" customHeight="true">
+      <c r="B4" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="22" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="122.25" customHeight="true">
+      <c r="B5" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="20" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="10" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="122.25" customHeight="true">
+      <c r="B6" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="23" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="10" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="122.25" customHeight="true">
+      <c r="B7" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7" t="s">
+      <c r="F7" s="18"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="19" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="122.25" customHeight="true">
+      <c r="B8" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="7" t="s">
+      <c r="F8" s="18"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="20" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="122.25" customHeight="true">
+      <c r="B9" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="10" t="s">
+      <c r="F9" s="18"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="22" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="106.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="122.25" customHeight="true">
+      <c r="B10" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="10" t="s">
+      <c r="F10" s="18"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="23" t="s">
         <v>153</v>
       </c>
     </row>
@@ -2389,7 +2408,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="73"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/함양 양잠가.xlsx
+++ b/sheets/민요/검수/함양 양잠가.xlsx
@@ -2187,13 +2187,13 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
   </cols>
   <sheetData>
